--- a/tests/SafeOpenXml.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Ra297dd8671b04f3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rb52e451be90744c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rd3f7a97f0b94472d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R0d19860c7367429e"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R4c2ad017c5ff4fda"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rcf8653d543fe45e6"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rd3f7a97f0b94472d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R0d19860c7367429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R9b839c9082f543ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R89cec5b702fd480c"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rcf8653d543fe45e6"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1f60245de9b84a9a"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
